--- a/03-Relatorios/01-Relatorio_Consolidado/dados/diagnostico-transversal-igovti-2026.xlsx
+++ b/03-Relatorios/01-Relatorio_Consolidado/dados/diagnostico-transversal-igovti-2026.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Universo e índices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faixas de maturidade" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmentos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Práticas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validações e limitações" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governança de TIC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Práticas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validações e limitações" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5397,7 +5398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5413,527 +5414,204 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>peso</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>mediana</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>respostas_validas</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>nao_aplicavel</t>
+          <t>minimo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>zeros_n</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zeros_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>abaixo_040_n</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>abaixo_040_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>q2201</t>
+          <t>q1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2201. A organização elabora um catálogo de serviços de tecnologia da informação e monitora níveis de serviço.</t>
+          <t>Modelo de gestão de TIC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1027433628318584</v>
+        <v>0.327403834851957</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.2059488692232055</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>0.05</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42</v>
+      </c>
+      <c r="I2" t="n">
+        <v>37.16814159292036</v>
+      </c>
+      <c r="J2" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80.53097345132744</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>q1003</t>
+          <t>q1002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1003. A instância superior de governança recebe serviços de auditoria interna que adicionam valor à organização.</t>
+          <t>Monitoramento do desempenho da gestão de TIC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1192477876106195</v>
+        <v>0.275682914168293</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.1268805309734513</v>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I3" t="n">
+        <v>61.06194690265486</v>
+      </c>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.49557522123894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>q2503</t>
+          <t>q1003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2503. A organização executa processo para classificação e tratamento de informações.</t>
+          <t>Atuação da auditoria interna em apoio à governança de TIC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1241150442477876</v>
+        <v>0.153597864756459</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.1192477876106195</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I4" t="n">
+        <v>58.4070796460177</v>
+      </c>
+      <c r="J4" t="n">
+        <v>104</v>
+      </c>
+      <c r="K4" t="n">
+        <v>92.03539823008849</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>q1002</t>
+          <t>q1004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1002. A alta administração monitora o desempenho da gestão de tecnologia da informação.</t>
+          <t>Simplificação dos serviços públicos</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1268805309734513</v>
+        <v>0.243315386223291</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.1862831858407079</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>q2203</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2203. A organização executa processo de gestão de configuração e ativos (de serviços de tecnologia da informação).</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.141740412979351</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E6" t="n">
-        <v>113</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>q2303</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2303. A organização executa processo de gestão de continuidade de serviços de tecnologia da informação.</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1528761061946902</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E7" t="n">
-        <v>113</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>q2301</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2301. A organização executa processo de gestão dos riscos de tecnologia da informação relativos a processos de negócio.</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.1535398230088496</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>113</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>q2202</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2202. A organização executa processo de gestão de mudanças.</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1721238938053097</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>113</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>q2204</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2204. A organização executa processo(s) de gestão de incidentes de serviços de tecnologia da informação e de incidentes de segurança da informação.</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1822271386430679</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E10" t="n">
-        <v>113</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>q2602</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2602. A organização executa processo de gestão de projetos de tecnologia da informação.</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1845132743362832</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>113</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>q1004</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1004. A organização definiu metas para a simplificação do atendimento prestado aos usuários dos serviços públicos.</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1862831858407079</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E12" t="n">
-        <v>113</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>q2302</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2302. A organização executa processo de gestão de riscos de segurança da informação.</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.188716814159292</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" t="n">
-        <v>113</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>q2601</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2601. A organização executa um processo de software.</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.2011061946902655</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E14" t="n">
-        <v>113</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>q2402</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2402. A organização dispõe de comitê de segurança da informação.</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.201216814159292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>113</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>q1001</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1001. A alta administração estabeleceu modelo de gestão de tecnologia da informação.</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2059488692232055</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E16" t="n">
-        <v>113</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>q2403</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2403. A organização possui um gestor institucional de segurança da informação.</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2268436578171091</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E17" t="n">
-        <v>113</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>q2504</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2504. A organização executa atividades de gestão da segurança dos recursos de processamento da informação, inclusive dos recursos de computação em nuvem.</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.2382139983909895</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E18" t="n">
-        <v>113</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>_q4251(TCU)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2501/2502. Gestão de ativos associados à informação e controle de acesso, conforme composição prevista na metodologia.</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.2408554572271386</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E19" t="n">
-        <v>113</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>q2102</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2102. A organização possui plano de tecnologia da informação vigente.</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.2961946902654867</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E20" t="n">
-        <v>113</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>q2101</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2101. A organização executa processo de planejamento de tecnologia da informação.</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.3141592920353982</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E21" t="n">
-        <v>113</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>q2401</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2401. A organização dispõe de uma política de segurança da informação.</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.3379646017699116</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E22" t="n">
-        <v>113</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4</v>
+      <c r="H5" t="n">
+        <v>51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>45.13274336283185</v>
+      </c>
+      <c r="J5" t="n">
+        <v>89</v>
+      </c>
+      <c r="K5" t="n">
+        <v>78.76106194690266</v>
       </c>
     </row>
   </sheetData>
@@ -5947,6 +5625,556 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mediana</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>respostas_validas</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>nao_aplicavel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>q2201</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2201. A organização elabora um catálogo de serviços de tecnologia da informação e monitora níveis de serviço.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1027433628318584</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>113</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>q1003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1003. A instância superior de governança recebe serviços de auditoria interna que adicionam valor à organização.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1192477876106195</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>113</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>q2503</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2503. A organização executa processo para classificação e tratamento de informações.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1241150442477876</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>113</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>q1002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1002. A alta administração monitora o desempenho da gestão de tecnologia da informação.</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1268805309734513</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>113</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2203. A organização executa processo de gestão de configuração e ativos (de serviços de tecnologia da informação).</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.141740412979351</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>113</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>q2303</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2303. A organização executa processo de gestão de continuidade de serviços de tecnologia da informação.</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1528761061946902</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>113</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>q2301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2301. A organização executa processo de gestão dos riscos de tecnologia da informação relativos a processos de negócio.</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1535398230088496</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>113</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>q2202</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2202. A organização executa processo de gestão de mudanças.</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1721238938053097</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>113</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>q2204</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2204. A organização executa processo(s) de gestão de incidentes de serviços de tecnologia da informação e de incidentes de segurança da informação.</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1822271386430679</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>113</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>q2602</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2602. A organização executa processo de gestão de projetos de tecnologia da informação.</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1845132743362832</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>113</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>q1004</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1004. A organização definiu metas para a simplificação do atendimento prestado aos usuários dos serviços públicos.</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1862831858407079</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>113</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>q2302</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2302. A organização executa processo de gestão de riscos de segurança da informação.</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.188716814159292</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>113</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>q2601</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2601. A organização executa um processo de software.</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2011061946902655</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>113</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>q2402</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2402. A organização dispõe de comitê de segurança da informação.</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.201216814159292</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>113</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>q1001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1001. A alta administração estabeleceu modelo de gestão de tecnologia da informação.</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2059488692232055</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E16" t="n">
+        <v>113</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>q2403</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2403. A organização possui um gestor institucional de segurança da informação.</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2268436578171091</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>113</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2504. A organização executa atividades de gestão da segurança dos recursos de processamento da informação, inclusive dos recursos de computação em nuvem.</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2382139983909895</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E18" t="n">
+        <v>113</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>_q4251(TCU)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2501/2502. Gestão de ativos associados à informação e controle de acesso, conforme composição prevista na metodologia.</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2408554572271386</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E19" t="n">
+        <v>113</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>q2102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2102. A organização possui plano de tecnologia da informação vigente.</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2961946902654867</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E20" t="n">
+        <v>113</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>q2101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2101. A organização executa processo de planejamento de tecnologia da informação.</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.3141592920353982</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>113</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>q2401</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2401. A organização dispõe de uma política de segurança da informação.</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.3379646017699116</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E22" t="n">
+        <v>113</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
